--- a/data/ams_weekly_data/Audio_Array/business_report_week27.xlsx
+++ b/data/ams_weekly_data/Audio_Array/business_report_week27.xlsx
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4304,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>248112.23</v>
+        <v>243708.84</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -10444,7 +10444,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -10456,7 +10456,7 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>28810.17</v>
+        <v>21607.63</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
